--- a/AAII_Financials/Yearly/CNM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNM_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/CNM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>CNM</t>
   </si>
@@ -656,50 +656,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45319</v>
+      </c>
+      <c r="E7" s="2">
         <v>44955</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44591</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44227</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43863</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43499</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -709,30 +709,33 @@
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>6702000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6651000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5004000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3642300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3388600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3201600</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -742,30 +745,33 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>4884000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4856000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3724000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2763900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2599400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2493500</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -775,30 +781,33 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1818000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1795000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1280000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>878400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>789200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>708100</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -808,9 +817,12 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,8 +836,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -856,9 +869,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -889,21 +905,24 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>51000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -919,33 +938,36 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E15" s="3">
         <v>140000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>138000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>137300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>125400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>112000</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
@@ -955,9 +977,12 @@
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -968,29 +993,30 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5962000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5876000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4630000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3456800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3233200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3063200</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1000,30 +1026,33 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>740000</v>
+      </c>
+      <c r="E18" s="3">
         <v>775000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>374000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>185500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>155400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>138400</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1033,9 +1062,12 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1049,8 +1081,9 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1069,8 +1102,8 @@
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1081,30 +1114,33 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>894000</v>
+      </c>
+      <c r="E21" s="3">
         <v>923000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>524000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>338200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>293600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>260700</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1114,30 +1150,33 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E22" s="3">
         <v>66000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>98000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>139100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>113700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>101100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1147,30 +1186,33 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>659000</v>
+      </c>
+      <c r="E23" s="3">
         <v>709000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>276000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>46400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>41700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>37300</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1180,9 +1222,12 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1190,20 +1235,20 @@
         <v>128000</v>
       </c>
       <c r="E24" s="3">
+        <v>128000</v>
+      </c>
+      <c r="F24" s="3">
         <v>51000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1213,9 +1258,12 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1246,30 +1294,33 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>531000</v>
+      </c>
+      <c r="E26" s="3">
         <v>581000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>225000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>44500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>41200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>36600</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1279,30 +1330,33 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>371000</v>
+      </c>
+      <c r="E27" s="3">
         <v>366000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>166000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>44500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>41200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>36600</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1312,9 +1366,12 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1345,9 +1402,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1378,9 +1438,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1411,9 +1474,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1444,9 +1510,12 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1465,8 +1534,8 @@
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1477,30 +1546,33 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>371000</v>
+      </c>
+      <c r="E33" s="3">
         <v>366000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>166000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>44500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>41200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>36600</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1510,9 +1582,12 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1543,30 +1618,33 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>371000</v>
+      </c>
+      <c r="E35" s="3">
         <v>366000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>166000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>44500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>41200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>36600</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1576,35 +1654,38 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45319</v>
+      </c>
+      <c r="E38" s="2">
         <v>44955</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44591</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44227</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43863</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43499</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1614,9 +1695,12 @@
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1630,8 +1714,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1645,26 +1730,27 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E41" s="3">
         <v>177000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>380900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>180900</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1677,9 +1763,12 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1710,27 +1799,30 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>973000</v>
+      </c>
+      <c r="E43" s="3">
         <v>955000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>884000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>556800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>504000</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1743,27 +1835,30 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>766000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1047000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>856000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>383800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>336100</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1776,27 +1871,30 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E45" s="3">
         <v>32000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>26000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>17100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,27 +1907,30 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1773000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2211000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1767000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1337100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1038100</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1842,9 +1943,12 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -1875,27 +1979,30 @@
       <c r="L47" s="3">
         <v>0</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>343000</v>
+      </c>
+      <c r="E48" s="3">
         <v>280000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>246000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>214700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>210900</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1908,27 +2015,30 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2345000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2330000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2386000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2371900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1948300</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1941,9 +2051,12 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1974,9 +2087,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2007,27 +2123,30 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>608000</v>
+      </c>
+      <c r="E52" s="3">
         <v>88000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>35000</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
       <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
         <v>2100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2040,9 +2159,12 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2073,27 +2195,30 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5069000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4909000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4434000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3923700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3199400</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2106,9 +2231,12 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2122,8 +2250,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2137,26 +2266,27 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>504000</v>
+      </c>
+      <c r="E57" s="3">
         <v>479000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>608000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>325700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>267600</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2169,9 +2299,12 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2182,13 +2315,13 @@
         <v>15000</v>
       </c>
       <c r="F58" s="3">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="G58" s="3">
         <v>13000</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="H58" s="3">
+        <v>13000</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
@@ -2202,27 +2335,30 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>255000</v>
+      </c>
+      <c r="E59" s="3">
         <v>232000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>216000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>183600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>149800</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2235,27 +2371,30 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>774000</v>
+      </c>
+      <c r="E60" s="3">
         <v>726000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>839000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>522300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>430400</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2268,27 +2407,30 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1863000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1444000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1456000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2251700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2011100</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2301,27 +2443,30 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>908000</v>
+      </c>
+      <c r="E62" s="3">
         <v>329000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>308000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>349000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>116400</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2334,9 +2479,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2367,9 +2515,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2400,9 +2551,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2433,27 +2587,30 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3618000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3162000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3109000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3123000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2557900</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2466,9 +2623,12 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2482,8 +2642,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2514,9 +2675,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2547,9 +2711,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2580,9 +2747,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2613,21 +2783,24 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>189000</v>
+      </c>
+      <c r="E72" s="3">
         <v>458000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>92000</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2643,12 +2816,15 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
+        <v>0</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2679,9 +2855,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2712,9 +2891,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2745,27 +2927,30 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1451000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1747000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1325000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>800700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>641500</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2778,9 +2963,12 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2811,35 +2999,38 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45319</v>
+      </c>
+      <c r="E80" s="2">
         <v>44955</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44591</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44227</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43863</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43499</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2849,30 +3040,33 @@
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>371000</v>
+      </c>
+      <c r="E81" s="3">
         <v>366000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>166000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>44500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>41200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>36600</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2882,9 +3076,12 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2898,29 +3095,30 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E83" s="3">
         <v>148000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>150000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>152700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>138200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>122300</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2930,9 +3128,12 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2963,9 +3164,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2996,9 +3200,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3029,9 +3236,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3062,9 +3272,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3095,30 +3308,33 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1069000</v>
+      </c>
+      <c r="E89" s="3">
         <v>401000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-31000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>219800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>206500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>100900</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3128,9 +3344,12 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3144,28 +3363,29 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11900</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-13900</v>
       </c>
       <c r="H91" s="3">
         <v>-13900</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
+      <c r="I91" s="3">
+        <v>-13900</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
@@ -3176,9 +3396,12 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3209,9 +3432,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3242,30 +3468,33 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-270000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-152000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-203000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-228900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-233600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21600</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,9 +3504,12 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3291,8 +3523,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3323,9 +3556,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3356,9 +3592,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3389,9 +3628,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3422,30 +3664,33 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-975000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-73000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-146000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>209100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>170700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-42100</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3455,9 +3700,12 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3488,30 +3736,33 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-176000</v>
+      </c>
+      <c r="E102" s="3">
         <v>176000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-380000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>143600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>37200</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3521,7 +3772,10 @@
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CNM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
   <si>
     <t>CNM</t>
   </si>
@@ -664,7 +664,8 @@
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -700,8 +701,8 @@
       <c r="I7" s="2">
         <v>43499</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="J7" s="2">
+        <v>38352</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -728,16 +729,16 @@
         <v>5004000</v>
       </c>
       <c r="G8" s="3">
-        <v>3642300</v>
+        <v>3642000</v>
       </c>
       <c r="H8" s="3">
-        <v>3388600</v>
+        <v>3389000</v>
       </c>
       <c r="I8" s="3">
         <v>3201600</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+      <c r="J8" s="3">
+        <v>1522100</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -764,16 +765,16 @@
         <v>3724000</v>
       </c>
       <c r="G9" s="3">
-        <v>2763900</v>
+        <v>2764000</v>
       </c>
       <c r="H9" s="3">
-        <v>2599400</v>
+        <v>2600000</v>
       </c>
       <c r="I9" s="3">
-        <v>2493500</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>2490800</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1212600</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -800,16 +801,16 @@
         <v>1280000</v>
       </c>
       <c r="G10" s="3">
-        <v>878400</v>
+        <v>878000</v>
       </c>
       <c r="H10" s="3">
-        <v>789200</v>
+        <v>789000</v>
       </c>
       <c r="I10" s="3">
-        <v>708100</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>710800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>309500</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -921,16 +922,16 @@
         <v>1000</v>
       </c>
       <c r="F14" s="3">
-        <v>51000</v>
+        <v>56000</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2700</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
@@ -960,16 +961,16 @@
         <v>138000</v>
       </c>
       <c r="G15" s="3">
-        <v>137300</v>
+        <v>137000</v>
       </c>
       <c r="H15" s="3">
-        <v>125400</v>
+        <v>125000</v>
       </c>
       <c r="I15" s="3">
         <v>112000</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+      <c r="J15" s="3">
+        <v>2400</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -1000,25 +1001,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5962000</v>
+        <v>5957000</v>
       </c>
       <c r="E17" s="3">
-        <v>5876000</v>
+        <v>5875000</v>
       </c>
       <c r="F17" s="3">
-        <v>4630000</v>
+        <v>4574000</v>
       </c>
       <c r="G17" s="3">
-        <v>3456800</v>
+        <v>3457000</v>
       </c>
       <c r="H17" s="3">
-        <v>3233200</v>
+        <v>3232000</v>
       </c>
       <c r="I17" s="3">
-        <v>3063200</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>3060500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1401400</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1036,25 +1037,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>740000</v>
+        <v>745000</v>
       </c>
       <c r="E18" s="3">
-        <v>775000</v>
+        <v>776000</v>
       </c>
       <c r="F18" s="3">
-        <v>374000</v>
+        <v>430000</v>
       </c>
       <c r="G18" s="3">
-        <v>185500</v>
+        <v>185000</v>
       </c>
       <c r="H18" s="3">
-        <v>155400</v>
+        <v>157000</v>
       </c>
       <c r="I18" s="3">
-        <v>138400</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>141100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>120700</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1087,26 +1088,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-400</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
@@ -1124,25 +1125,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>894000</v>
+        <v>892000</v>
       </c>
       <c r="E21" s="3">
-        <v>923000</v>
+        <v>916000</v>
       </c>
       <c r="F21" s="3">
-        <v>524000</v>
+        <v>568000</v>
       </c>
       <c r="G21" s="3">
-        <v>338200</v>
+        <v>322000</v>
       </c>
       <c r="H21" s="3">
-        <v>293600</v>
+        <v>282000</v>
       </c>
       <c r="I21" s="3">
-        <v>260700</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>253100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>123400</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1169,16 +1170,16 @@
         <v>98000</v>
       </c>
       <c r="G22" s="3">
-        <v>139100</v>
+        <v>139000</v>
       </c>
       <c r="H22" s="3">
-        <v>113700</v>
+        <v>113000</v>
       </c>
       <c r="I22" s="3">
         <v>101100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>35100</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1205,16 +1206,16 @@
         <v>276000</v>
       </c>
       <c r="G23" s="3">
-        <v>46400</v>
+        <v>46000</v>
       </c>
       <c r="H23" s="3">
-        <v>41700</v>
+        <v>42000</v>
       </c>
       <c r="I23" s="3">
         <v>37300</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+      <c r="J23" s="3">
+        <v>85900</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1241,16 +1242,16 @@
         <v>51000</v>
       </c>
       <c r="G24" s="3">
-        <v>1900</v>
+        <v>9000</v>
       </c>
       <c r="H24" s="3">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>34700</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1313,16 +1314,16 @@
         <v>225000</v>
       </c>
       <c r="G26" s="3">
-        <v>44500</v>
+        <v>37000</v>
       </c>
       <c r="H26" s="3">
-        <v>41200</v>
+        <v>36000</v>
       </c>
       <c r="I26" s="3">
         <v>36600</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+      <c r="J26" s="3">
+        <v>51200</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1346,19 +1347,19 @@
         <v>366000</v>
       </c>
       <c r="F27" s="3">
-        <v>166000</v>
+        <v>90000</v>
       </c>
       <c r="G27" s="3">
-        <v>44500</v>
+        <v>37000</v>
       </c>
       <c r="H27" s="3">
-        <v>41200</v>
+        <v>36000</v>
       </c>
       <c r="I27" s="3">
         <v>36600</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+      <c r="J27" s="3">
+        <v>51200</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1519,26 +1520,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
+        <v>400</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
@@ -1565,16 +1566,16 @@
         <v>166000</v>
       </c>
       <c r="G33" s="3">
-        <v>44500</v>
+        <v>37000</v>
       </c>
       <c r="H33" s="3">
-        <v>41200</v>
+        <v>36000</v>
       </c>
       <c r="I33" s="3">
         <v>36600</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+      <c r="J33" s="3">
+        <v>51200</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1637,16 +1638,16 @@
         <v>166000</v>
       </c>
       <c r="G35" s="3">
-        <v>44500</v>
+        <v>37000</v>
       </c>
       <c r="H35" s="3">
-        <v>41200</v>
+        <v>36000</v>
       </c>
       <c r="I35" s="3">
         <v>36600</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+      <c r="J35" s="3">
+        <v>51200</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1686,8 +1687,8 @@
       <c r="I38" s="2">
         <v>43499</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="J38" s="2">
+        <v>38352</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1746,7 +1747,7 @@
         <v>1000</v>
       </c>
       <c r="G41" s="3">
-        <v>380900</v>
+        <v>381000</v>
       </c>
       <c r="H41" s="3">
         <v>180900</v>
@@ -1754,8 +1755,8 @@
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="J41" s="3">
+        <v>15900</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1818,7 +1819,7 @@
         <v>884000</v>
       </c>
       <c r="G43" s="3">
-        <v>556800</v>
+        <v>557000</v>
       </c>
       <c r="H43" s="3">
         <v>504000</v>
@@ -1826,8 +1827,8 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="J43" s="3">
+        <v>227800</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -1854,7 +1855,7 @@
         <v>856000</v>
       </c>
       <c r="G44" s="3">
-        <v>383800</v>
+        <v>384000</v>
       </c>
       <c r="H44" s="3">
         <v>336100</v>
@@ -1862,8 +1863,8 @@
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+      <c r="J44" s="3">
+        <v>126900</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>3</v>
@@ -1880,26 +1881,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>33000</v>
-      </c>
-      <c r="E45" s="3">
-        <v>32000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>26000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>15600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>17100</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+      <c r="J45" s="3">
+        <v>2700</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
@@ -1926,7 +1927,7 @@
         <v>1767000</v>
       </c>
       <c r="G46" s="3">
-        <v>1337100</v>
+        <v>1337000</v>
       </c>
       <c r="H46" s="3">
         <v>1038100</v>
@@ -1934,8 +1935,8 @@
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+      <c r="J46" s="3">
+        <v>374700</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
@@ -1953,25 +1954,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>31000</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -1998,16 +1999,16 @@
         <v>246000</v>
       </c>
       <c r="G48" s="3">
-        <v>214700</v>
+        <v>213000</v>
       </c>
       <c r="H48" s="3">
-        <v>210900</v>
+        <v>206300</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="J48" s="3">
+        <v>19300</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2034,16 +2035,16 @@
         <v>2386000</v>
       </c>
       <c r="G49" s="3">
-        <v>2371900</v>
+        <v>2374000</v>
       </c>
       <c r="H49" s="3">
-        <v>1948300</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>1952900</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>457200</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2132,17 +2133,17 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>608000</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E52" s="3">
-        <v>88000</v>
+        <v>4000</v>
       </c>
       <c r="F52" s="3">
-        <v>35000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
+        <v>4000</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
         <v>2100</v>
@@ -2150,8 +2151,8 @@
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>3000</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2214,7 +2215,7 @@
         <v>4434000</v>
       </c>
       <c r="G54" s="3">
-        <v>3923700</v>
+        <v>3924000</v>
       </c>
       <c r="H54" s="3">
         <v>3199400</v>
@@ -2222,8 +2223,8 @@
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+      <c r="J54" s="3">
+        <v>874700</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2282,7 +2283,7 @@
         <v>608000</v>
       </c>
       <c r="G57" s="3">
-        <v>325700</v>
+        <v>326000</v>
       </c>
       <c r="H57" s="3">
         <v>267600</v>
@@ -2290,8 +2291,8 @@
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="J57" s="3">
+        <v>172200</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
@@ -2309,25 +2310,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>69000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>64000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>56000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>52800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>15000</v>
-      </c>
-      <c r="E58" s="3">
-        <v>15000</v>
-      </c>
-      <c r="F58" s="3">
-        <v>15000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>13000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>13000</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2345,25 +2346,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>255000</v>
+        <v>94000</v>
       </c>
       <c r="E59" s="3">
-        <v>232000</v>
+        <v>55000</v>
       </c>
       <c r="F59" s="3">
-        <v>216000</v>
+        <v>58000</v>
       </c>
       <c r="G59" s="3">
-        <v>183600</v>
+        <v>22000</v>
       </c>
       <c r="H59" s="3">
-        <v>149800</v>
+        <v>16000</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+      <c r="J59" s="3">
+        <v>2900</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2390,7 +2391,7 @@
         <v>839000</v>
       </c>
       <c r="G60" s="3">
-        <v>522300</v>
+        <v>522000</v>
       </c>
       <c r="H60" s="3">
         <v>430400</v>
@@ -2398,8 +2399,8 @@
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+      <c r="J60" s="3">
+        <v>233600</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
@@ -2417,25 +2418,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1863000</v>
+        <v>2001000</v>
       </c>
       <c r="E61" s="3">
-        <v>1444000</v>
+        <v>1565000</v>
       </c>
       <c r="F61" s="3">
-        <v>1456000</v>
+        <v>1559000</v>
       </c>
       <c r="G61" s="3">
-        <v>2251700</v>
+        <v>2338000</v>
       </c>
       <c r="H61" s="3">
-        <v>2011100</v>
+        <v>2094700</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>395000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2453,25 +2454,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>908000</v>
+        <v>722000</v>
       </c>
       <c r="E62" s="3">
-        <v>329000</v>
+        <v>199000</v>
       </c>
       <c r="F62" s="3">
-        <v>308000</v>
+        <v>170000</v>
       </c>
       <c r="G62" s="3">
-        <v>349000</v>
+        <v>31000</v>
       </c>
       <c r="H62" s="3">
-        <v>116400</v>
+        <v>31000</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+      <c r="J62" s="3">
+        <v>3100</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -2597,13 +2598,13 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3618000</v>
+        <v>3545000</v>
       </c>
       <c r="E66" s="3">
-        <v>3162000</v>
+        <v>2499000</v>
       </c>
       <c r="F66" s="3">
-        <v>3109000</v>
+        <v>2603000</v>
       </c>
       <c r="G66" s="3">
         <v>3123000</v>
@@ -2614,8 +2615,8 @@
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+      <c r="J66" s="3">
+        <v>654900</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2810,8 +2811,8 @@
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="J72" s="3">
+        <v>20200</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2946,7 +2947,7 @@
         <v>1325000</v>
       </c>
       <c r="G76" s="3">
-        <v>800700</v>
+        <v>801000</v>
       </c>
       <c r="H76" s="3">
         <v>641500</v>
@@ -2954,8 +2955,8 @@
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="J76" s="3">
+        <v>219800</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -3031,8 +3032,8 @@
       <c r="I80" s="2">
         <v>43499</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="J80" s="2">
+        <v>38352</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -3059,16 +3060,16 @@
         <v>166000</v>
       </c>
       <c r="G81" s="3">
-        <v>44500</v>
+        <v>37000</v>
       </c>
       <c r="H81" s="3">
-        <v>41200</v>
+        <v>36000</v>
       </c>
       <c r="I81" s="3">
         <v>36600</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+      <c r="J81" s="3">
+        <v>51200</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3102,25 +3103,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>154000</v>
+        <v>32000</v>
       </c>
       <c r="E83" s="3">
-        <v>148000</v>
+        <v>28000</v>
       </c>
       <c r="F83" s="3">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="G83" s="3">
-        <v>152700</v>
+        <v>35000</v>
       </c>
       <c r="H83" s="3">
-        <v>138200</v>
+        <v>31000</v>
       </c>
       <c r="I83" s="3">
-        <v>122300</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>26400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>2400</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3327,16 +3328,16 @@
         <v>-31000</v>
       </c>
       <c r="G89" s="3">
-        <v>219800</v>
+        <v>214000</v>
       </c>
       <c r="H89" s="3">
-        <v>206500</v>
+        <v>194000</v>
       </c>
       <c r="I89" s="3">
         <v>100900</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+      <c r="J89" s="3">
+        <v>61400</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3379,16 +3380,16 @@
         <v>-20000</v>
       </c>
       <c r="G91" s="3">
-        <v>-11900</v>
+        <v>-12000</v>
       </c>
       <c r="H91" s="3">
-        <v>-13900</v>
+        <v>-14000</v>
       </c>
       <c r="I91" s="3">
         <v>-13900</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+      <c r="J91" s="3">
+        <v>-1400</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>3</v>
@@ -3487,16 +3488,16 @@
         <v>-203000</v>
       </c>
       <c r="G94" s="3">
-        <v>-228900</v>
+        <v>-229000</v>
       </c>
       <c r="H94" s="3">
-        <v>-233600</v>
+        <v>-234000</v>
       </c>
       <c r="I94" s="3">
         <v>-21600</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3">
+        <v>-2800</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3545,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>25400</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>31400</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -3683,16 +3684,16 @@
         <v>-146000</v>
       </c>
       <c r="G100" s="3">
-        <v>209100</v>
+        <v>215000</v>
       </c>
       <c r="H100" s="3">
-        <v>170700</v>
+        <v>184000</v>
       </c>
       <c r="I100" s="3">
         <v>-42100</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="J100" s="3">
+        <v>-61400</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3709,26 +3710,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -3758,13 +3759,13 @@
         <v>200000</v>
       </c>
       <c r="H102" s="3">
-        <v>143600</v>
+        <v>144000</v>
       </c>
       <c r="I102" s="3">
         <v>37200</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="J102" s="3">
+        <v>-2800</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/CNM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>CNM</t>
   </si>
@@ -656,174 +656,187 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E7" s="2">
         <v>45319</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44955</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44591</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43863</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43499</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>38352</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7441000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6702000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6651000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5004000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3642000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3389000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3201600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1522100</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5461000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4884000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4856000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3724000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2764000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2600000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2490800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1212600</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1980000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1818000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1795000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1280000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>878000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>789000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>710800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>309500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,8 +851,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -873,9 +887,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -909,81 +926,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>5000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3">
         <v>56000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>2000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2700</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>183000</v>
+      </c>
+      <c r="E15" s="3">
         <v>147000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>140000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>138000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>137000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>125000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>112000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2400</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -995,80 +1021,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5957000</v>
+        <v>6722000</v>
       </c>
       <c r="E17" s="3">
-        <v>5875000</v>
+        <v>5962000</v>
       </c>
       <c r="F17" s="3">
+        <v>5876000</v>
+      </c>
+      <c r="G17" s="3">
         <v>4574000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3457000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3232000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3060500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1401400</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>745000</v>
+        <v>719000</v>
       </c>
       <c r="E18" s="3">
-        <v>776000</v>
+        <v>740000</v>
       </c>
       <c r="F18" s="3">
+        <v>775000</v>
+      </c>
+      <c r="G18" s="3">
         <v>430000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>185000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>157000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>141100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>120700</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1083,8 +1116,9 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1106,165 +1140,180 @@
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>892000</v>
+        <v>902000</v>
       </c>
       <c r="E21" s="3">
-        <v>916000</v>
+        <v>887000</v>
       </c>
       <c r="F21" s="3">
+        <v>915000</v>
+      </c>
+      <c r="G21" s="3">
         <v>568000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>322000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>282000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>253100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>123400</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E22" s="3">
         <v>81000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>66000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>98000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>139000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>113000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>101100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>35100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>577000</v>
+      </c>
+      <c r="E23" s="3">
         <v>659000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>709000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>276000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>46000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>42000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>37300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>85900</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>128000</v>
+        <v>143000</v>
       </c>
       <c r="E24" s="3">
         <v>128000</v>
       </c>
       <c r="F24" s="3">
+        <v>128000</v>
+      </c>
+      <c r="G24" s="3">
         <v>51000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>34700</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1298,81 +1347,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>434000</v>
+      </c>
+      <c r="E26" s="3">
         <v>531000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>581000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>225000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>37000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>36000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>36600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>51200</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>411000</v>
+      </c>
+      <c r="E27" s="3">
         <v>371000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>366000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>90000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>37000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>36000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>36600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>51200</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1406,9 +1464,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1442,9 +1503,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1478,9 +1542,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1514,9 +1581,12 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1538,57 +1608,63 @@
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>411000</v>
+      </c>
+      <c r="E33" s="3">
         <v>371000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>366000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>166000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>37000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>36000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>36600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>51200</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1622,86 +1698,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>411000</v>
+      </c>
+      <c r="E35" s="3">
         <v>371000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>366000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>166000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>37000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>36000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>36600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>51200</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E38" s="2">
         <v>45319</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44955</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44591</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43863</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43499</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>38352</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1716,8 +1801,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1732,44 +1818,48 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>177000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>381000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>180900</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3">
         <v>15900</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1803,81 +1893,90 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1066000</v>
+      </c>
+      <c r="E43" s="3">
         <v>973000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>955000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>884000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>557000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>504000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K43" s="3">
         <v>227800</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>908000</v>
+      </c>
+      <c r="E44" s="3">
         <v>766000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1047000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>856000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>384000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>336100</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K44" s="3">
         <v>126900</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1899,72 +1998,78 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>2700</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2025000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1773000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2211000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1767000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1337000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1038100</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="3">
         <v>374700</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>67000</v>
+        <v>40000</v>
       </c>
       <c r="E47" s="3">
+        <v>66000</v>
+      </c>
+      <c r="F47" s="3">
         <v>84000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>31000</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1974,8 +2079,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -1983,81 +2088,90 @@
       <c r="M47" s="3">
         <v>0</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>412000</v>
+      </c>
+      <c r="E48" s="3">
         <v>343000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>280000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>246000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>213000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>206300</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K48" s="3">
         <v>19300</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2833000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2345000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2330000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2386000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2374000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1952900</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>457200</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2091,9 +2205,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2127,45 +2244,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3">
-        <v>4000</v>
+      <c r="D52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>4000</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="G52" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3">
         <v>2100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
         <v>3000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2199,45 +2322,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5870000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5069000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4909000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4434000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3924000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3199400</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K54" s="3">
         <v>874700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2252,8 +2381,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2268,224 +2398,243 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>562000</v>
+      </c>
+      <c r="E57" s="3">
         <v>504000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>479000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>608000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>326000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>267600</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3">
         <v>172200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E58" s="3">
         <v>70000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>69000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>64000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>56000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>52800</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>15000</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>90000</v>
+      </c>
+      <c r="E59" s="3">
         <v>94000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>55000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>58000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>2900</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>866000</v>
+      </c>
+      <c r="E60" s="3">
         <v>774000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>726000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>839000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>522000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>430400</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3">
         <v>233600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2415000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2001000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1565000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1559000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2338000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2094700</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>395000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>728000</v>
+      </c>
+      <c r="E62" s="3">
         <v>722000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>199000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>170000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>31000</v>
       </c>
       <c r="H62" s="3">
         <v>31000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="I62" s="3">
+        <v>31000</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>3100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2519,9 +2668,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2555,9 +2707,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2591,45 +2746,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4096000</v>
+      </c>
+      <c r="E66" s="3">
         <v>3545000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2499000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2603000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3123000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2557900</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K66" s="3">
         <v>654900</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2644,8 +2805,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2679,9 +2841,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2715,9 +2880,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2751,9 +2919,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2787,45 +2958,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>449000</v>
+      </c>
+      <c r="E72" s="3">
         <v>189000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>458000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>92000</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>20200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2859,9 +3036,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2895,9 +3075,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2931,45 +3114,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1698000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1451000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1747000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1325000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>801000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>641500</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K76" s="3">
         <v>219800</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3003,86 +3192,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45690</v>
+      </c>
+      <c r="E80" s="2">
         <v>45319</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44955</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44591</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43863</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43499</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>38352</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>411000</v>
+      </c>
+      <c r="E81" s="3">
         <v>371000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>366000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>166000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>37000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>36000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>36600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>51200</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3097,44 +3295,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E83" s="3">
         <v>32000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>28000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>35000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>26400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2400</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3168,9 +3370,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3204,9 +3409,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3240,9 +3448,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3276,9 +3487,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3312,45 +3526,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>621000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1069000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>401000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-31000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>214000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>194000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>100900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>61400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3365,44 +3585,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-39000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-14000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3436,9 +3660,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3472,45 +3699,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-788000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-270000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-152000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-203000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-229000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-234000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-21600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2800</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3525,8 +3758,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3546,23 +3780,26 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>25400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>31400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3596,9 +3833,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3632,9 +3872,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3668,45 +3911,51 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-975000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-73000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-146000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>215000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>184000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-42100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-61400</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3731,8 +3980,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -3740,43 +3989,49 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-176000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>176000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-380000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>200000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>144000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>37200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2800</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CNM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="92">
   <si>
     <t>CNM</t>
   </si>
@@ -656,187 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E7" s="2">
         <v>45690</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45319</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44955</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44591</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44227</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43863</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43499</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>38352</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7647000</v>
+      </c>
+      <c r="E8" s="3">
         <v>7441000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6702000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6651000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5004000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3642000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3389000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3201600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1522100</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5588000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5461000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4884000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4856000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3724000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2764000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2600000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2490800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1212600</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2059000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1980000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1818000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1795000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1280000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>878000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>789000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>710800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>309500</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -852,8 +864,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -890,9 +903,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -929,9 +945,12 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -944,33 +963,36 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
         <v>56000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -978,38 +1000,41 @@
         <v>183000</v>
       </c>
       <c r="E15" s="3">
+        <v>183000</v>
+      </c>
+      <c r="F15" s="3">
         <v>147000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>140000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>138000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>137000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>125000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>112000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2400</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1022,86 +1047,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6925000</v>
+      </c>
+      <c r="E17" s="3">
         <v>6722000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5962000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5876000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4574000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3457000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3232000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3060500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1401400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>722000</v>
+      </c>
+      <c r="E18" s="3">
         <v>719000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>740000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>775000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>430000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>185000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>157000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>141100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>120700</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1117,13 +1149,14 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-5000</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
@@ -1143,177 +1176,192 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>910000</v>
+      </c>
+      <c r="E21" s="3">
         <v>902000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>887000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>915000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>568000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>322000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>282000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>253100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>123400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E22" s="3">
         <v>142000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>81000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>66000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>98000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>139000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>113000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>101100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>35100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>607000</v>
+      </c>
+      <c r="E23" s="3">
         <v>577000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>659000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>709000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>276000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>46000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>42000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>37300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>85900</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>145000</v>
+      </c>
+      <c r="E24" s="3">
         <v>143000</v>
-      </c>
-      <c r="E24" s="3">
-        <v>128000</v>
       </c>
       <c r="F24" s="3">
         <v>128000</v>
       </c>
       <c r="G24" s="3">
+        <v>128000</v>
+      </c>
+      <c r="H24" s="3">
         <v>51000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>34700</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1350,87 +1398,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>462000</v>
+      </c>
+      <c r="E26" s="3">
         <v>434000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>531000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>581000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>225000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>37000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>36000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>36600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>51200</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>441000</v>
+      </c>
+      <c r="E27" s="3">
         <v>411000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>371000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>366000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>90000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>37000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>36000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>36600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>51200</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1467,9 +1524,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1506,9 +1566,12 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1545,9 +1608,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1584,14 +1650,17 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>5000</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>3</v>
@@ -1611,60 +1680,66 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>441000</v>
+      </c>
+      <c r="E33" s="3">
         <v>411000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>371000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>366000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>166000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>37000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>36000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>36600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>51200</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1701,92 +1776,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>441000</v>
+      </c>
+      <c r="E35" s="3">
         <v>411000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>371000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>366000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>166000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>37000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>36000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>36600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>51200</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E38" s="2">
         <v>45690</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45319</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44955</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44591</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44227</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43863</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43499</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>38352</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1802,8 +1886,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1819,52 +1904,56 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E41" s="3">
         <v>8000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>177000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>381000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>180900</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3">
         <v>15900</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -1896,87 +1985,96 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1048000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1066000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>973000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>955000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>884000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>557000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>504000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
         <v>227800</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>986000</v>
+      </c>
+      <c r="E44" s="3">
         <v>908000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>766000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1047000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>856000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>384000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>336100</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3">
         <v>126900</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2001,78 +2099,84 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>2700</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2302000</v>
+      </c>
+      <c r="E46" s="3">
         <v>2025000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1773000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2211000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1767000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1337000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1038100</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3">
         <v>374700</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E47" s="3">
         <v>40000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>66000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>84000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>31000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2082,8 +2186,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2091,87 +2195,96 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>465000</v>
+      </c>
+      <c r="E48" s="3">
         <v>412000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>343000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>280000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>246000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>213000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>206300</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3">
         <v>19300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2743000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2833000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2345000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2330000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2386000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2374000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1952900</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>457200</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2208,9 +2321,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2247,48 +2363,54 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E52" s="3">
         <v>2000</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3">
-        <v>4000</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G52" s="3">
         <v>4000</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="H52" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>2100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>3000</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2325,48 +2447,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6085000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5870000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5069000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4909000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4434000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3924000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3199400</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3">
         <v>874700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2382,8 +2510,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2399,242 +2528,261 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>512000</v>
+      </c>
+      <c r="E57" s="3">
         <v>562000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>504000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>479000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>608000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>326000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>267600</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
         <v>172200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E58" s="3">
         <v>91000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>70000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>69000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>64000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>56000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>52800</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>15000</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E59" s="3">
         <v>90000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>94000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>55000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>58000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>2900</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>874000</v>
+      </c>
+      <c r="E60" s="3">
         <v>866000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>774000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>726000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>839000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>522000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>430400</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3">
         <v>233600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2338000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2415000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2001000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1565000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1559000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2338000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2094700</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>395000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>710000</v>
+      </c>
+      <c r="E62" s="3">
         <v>728000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>722000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>199000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>170000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>31000</v>
       </c>
       <c r="I62" s="3">
         <v>31000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="J62" s="3">
+        <v>31000</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>3100</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2671,9 +2819,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2710,9 +2861,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2749,48 +2903,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4011000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4096000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3545000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2499000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2603000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3123000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2557900</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3">
         <v>654900</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2806,8 +2966,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2844,9 +3005,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2883,9 +3047,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2922,9 +3089,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2961,48 +3131,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>755000</v>
+      </c>
+      <c r="E72" s="3">
         <v>449000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>189000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>458000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>92000</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
         <v>20200</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3">
+        <v>0</v>
+      </c>
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3039,9 +3215,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3078,9 +3257,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3117,48 +3299,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1997000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1698000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1451000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1747000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1325000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>801000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>641500</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3">
         <v>219800</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3195,92 +3383,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46054</v>
+      </c>
+      <c r="E80" s="2">
         <v>45690</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45319</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44955</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44591</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44227</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43863</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43499</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>38352</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>441000</v>
+      </c>
+      <c r="E81" s="3">
         <v>411000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>371000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>366000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>166000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>37000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>36000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>36600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>51200</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3296,8 +3493,9 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3305,38 +3503,41 @@
         <v>43000</v>
       </c>
       <c r="E83" s="3">
+        <v>43000</v>
+      </c>
+      <c r="F83" s="3">
         <v>32000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>28000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>30000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>35000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>31000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2400</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3373,9 +3574,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3412,9 +3616,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3451,9 +3658,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3490,9 +3700,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3529,48 +3742,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>650000</v>
+      </c>
+      <c r="E89" s="3">
         <v>621000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1069000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>401000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-31000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>214000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>194000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>100900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>61400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3586,47 +3805,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-46000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-35000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-39000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-20000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1400</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3663,9 +3886,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3702,48 +3928,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-145000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-788000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-270000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-152000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-203000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-229000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-234000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-21600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2800</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3759,8 +3991,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3783,23 +4016,26 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>25400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>31400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3836,9 +4072,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3875,9 +4114,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3914,48 +4156,54 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-293000</v>
+      </c>
+      <c r="E100" s="3">
         <v>174000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-975000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-73000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-146000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>215000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>184000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-42100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-61400</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3983,8 +4231,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -3992,46 +4240,52 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E102" s="3">
         <v>7000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-176000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>176000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-380000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>200000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>144000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>37200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2800</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
